--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -1326,19 +1326,83 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
+      <c r="B16" s="9" t="n">
+        <v>9201</v>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>AutoChessPlayerAttackDamage</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>AutoChess player attack health damage</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>9001;1;12.0;3</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>9301</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
+      <c r="B17" s="9" t="n">
+        <v>9202</v>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>AutoChessEnemyAttackDamage</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>AutoChess enemy attack health damage</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>9001;1;8.0;3</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>9301</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
+      <c r="B18" s="9" t="n">
+        <v>9207</v>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>AutoChessPlayerExecute</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>AutoChess execute command marker</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>9301</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="9" t="n"/>

--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayEffect.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK26"/>
+  <dimension ref="A1:AK28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col width="12.21875" customWidth="1" min="3" max="4"/>
@@ -1432,6 +1432,101 @@
     <row r="26">
       <c r="B26" s="9" t="n"/>
     </row>
+    <row r="27">
+      <c r="B27" s="9" t="n">
+        <v>9203</v>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>AutoChessPlayerPoison</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>AutoChess player periodic poison active effect</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>8</v>
+      </c>
+      <c r="M27" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>9204</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>9301</t>
+        </is>
+      </c>
+      <c r="Y27" t="n">
+        <v>9203</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="9" t="n">
+        <v>9204</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>AutoChessPoisonTickDamage</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>AutoChess poison period tick health damage</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>9001;1;1.0;3</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>9301</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="K2:M2"/>
